--- a/test/excel/xlsx/saved/arrays-7.xlsx
+++ b/test/excel/xlsx/saved/arrays-7.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11004"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBDF5169-F0E9-B349-8E08-FD46F4FD424F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4AE212B-4217-8A4B-A83D-06FA60B2B296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="78">
   <si>
     <t>Ann</t>
   </si>
@@ -214,6 +214,18 @@
   </si>
   <si>
     <t>1,5</t>
+  </si>
+  <si>
+    <t>lift:YIELD#13</t>
+  </si>
+  <si>
+    <t>lift:YIELD#14</t>
+  </si>
+  <si>
+    <t>lift:YIELDDISC#1</t>
+  </si>
+  <si>
+    <t>lift:YIELDDISC#2</t>
   </si>
   <si>
     <t>lift:YIELDDISC#3</t>
@@ -1914,24 +1926,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="e" cm="1">
-        <f t="array" ref="A1">YIELDDISC(DATE(2008,2,16),D!B1:B2,99.795,100,2)</f>
+        <f t="array" ref="A1">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,95.04287,100,2,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B1">
-        <f t="shared" ref="B1:B24" si="0">IF(ISERROR(A1),ERROR.TYPE(A1),IF(ISNUMBER(A1),0,IF(ISLOGICAL(A1),IF(A1,-1,-2),IF(ISTEXT(A1),-3,-4))))</f>
+        <f t="shared" ref="B1:B28" si="0">IF(ISERROR(A1),ERROR.TYPE(A1),IF(ISNUMBER(A1),0,IF(ISLOGICAL(A1),IF(A1,-1,-2),IF(ISTEXT(A1),-3,-4))))</f>
         <v>3</v>
       </c>
       <c r="C1">
-        <f t="shared" ref="C1:C24" si="1">IF(ISNUMBER(A1),A1,0)</f>
+        <f t="shared" ref="C1:C28" si="1">IF(ISNUMBER(A1),A1,0)</f>
         <v>0</v>
       </c>
       <c r="D1" t="str">
-        <f t="shared" ref="D1:D24" si="2">IF(ISTEXT(A1),A1,"")</f>
+        <f t="shared" ref="D1:D28" si="2">IF(ISTEXT(A1),A1,"")</f>
         <v/>
       </c>
       <c r="E1" t="s">
@@ -1940,7 +1952,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A2" ca="1">YIELDDISC(DATE(2008,2,16),{1;2},99.795,100,2)</f>
+        <f t="array" aca="1" ref="A2" ca="1">YIELD(DATE(2008,2,15),DATE(2016,11,15),0.0575,95.04287,100,2,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B2">
@@ -1961,7 +1973,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="e" cm="1">
-        <f t="array" ref="A3">YIELDDISC(DATE(2008,2,16),DATE(2008,3,1),D!B1:B2,100,2)</f>
+        <f t="array" ref="A3">YIELDDISC(D!B1:B2,DATE(2008,3,1),99.795,100,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B3">
@@ -1982,7 +1994,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A4" ca="1">YIELDDISC(DATE(2008,2,16),DATE(2008,3,1),{1;2},100,2)</f>
+        <f t="array" aca="1" ref="A4" ca="1">YIELDDISC({1;2},DATE(2008,3,1),99.795,100,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B4">
@@ -2003,7 +2015,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="e" cm="1">
-        <f t="array" ref="A5">YIELDDISC(DATE(2008,2,16),DATE(2008,3,1),99.795,D!B1:B2,2)</f>
+        <f t="array" ref="A5">YIELDDISC(DATE(2008,2,16),D!B1:B2,99.795,100,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B5">
@@ -2024,7 +2036,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A6" ca="1">YIELDDISC(DATE(2008,2,16),DATE(2008,3,1),99.795,{1;2},2)</f>
+        <f t="array" aca="1" ref="A6" ca="1">YIELDDISC(DATE(2008,2,16),{1;2},99.795,100,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B6">
@@ -2045,7 +2057,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="e" cm="1">
-        <f t="array" ref="A7">YIELDDISC(DATE(2008,2,16),DATE(2008,3,1),99.795,100,D!B1:B2)</f>
+        <f t="array" ref="A7">YIELDDISC(DATE(2008,2,16),DATE(2008,3,1),D!B1:B2,100,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B7">
@@ -2066,7 +2078,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A8" ca="1">YIELDDISC(DATE(2008,2,16),DATE(2008,3,1),99.795,100,{1;2})</f>
+        <f t="array" aca="1" ref="A8" ca="1">YIELDDISC(DATE(2008,2,16),DATE(2008,3,1),{1;2},100,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B8">
@@ -2087,7 +2099,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="e" cm="1">
-        <f t="array" ref="A9">YIELDMAT(D!B1:B2,DATE(2008,11,3),DATE(2007,11,8),0.0625,100.0123,0)</f>
+        <f t="array" ref="A9">YIELDDISC(DATE(2008,2,16),DATE(2008,3,1),99.795,D!B1:B2,2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B9">
@@ -2108,7 +2120,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A10" ca="1">YIELDMAT({1;2},DATE(2008,11,3),DATE(2007,11,8),0.0625,100.0123,0)</f>
+        <f t="array" aca="1" ref="A10" ca="1">YIELDDISC(DATE(2008,2,16),DATE(2008,3,1),99.795,{1;2},2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B10">
@@ -2129,7 +2141,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="e" cm="1">
-        <f t="array" ref="A11">YIELDMAT(DATE(2008,3,15),D!B1:B2,DATE(2007,11,8),0.0625,100.0123,0)</f>
+        <f t="array" ref="A11">YIELDDISC(DATE(2008,2,16),DATE(2008,3,1),99.795,100,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B11">
@@ -2150,7 +2162,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A12" ca="1">YIELDMAT(DATE(2008,3,15),{1;2},DATE(2007,11,8),0.0625,100.0123,0)</f>
+        <f t="array" aca="1" ref="A12" ca="1">YIELDDISC(DATE(2008,2,16),DATE(2008,3,1),99.795,100,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B12">
@@ -2171,7 +2183,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="e" cm="1">
-        <f t="array" ref="A13">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),D!B1:B2,0.0625,100.0123,0)</f>
+        <f t="array" ref="A13">YIELDMAT(D!B1:B2,DATE(2008,11,3),DATE(2007,11,8),0.0625,100.0123,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B13">
@@ -2192,7 +2204,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A14" ca="1">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),{1;2},0.0625,100.0123,0)</f>
+        <f t="array" aca="1" ref="A14" ca="1">YIELDMAT({1;2},DATE(2008,11,3),DATE(2007,11,8),0.0625,100.0123,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B14">
@@ -2213,7 +2225,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="e" cm="1">
-        <f t="array" ref="A15">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),DATE(2007,11,8),D!B1:B2,100.0123,0)</f>
+        <f t="array" ref="A15">YIELDMAT(DATE(2008,3,15),D!B1:B2,DATE(2007,11,8),0.0625,100.0123,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B15">
@@ -2234,7 +2246,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A16" ca="1">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),DATE(2007,11,8),{1;2},100.0123,0)</f>
+        <f t="array" aca="1" ref="A16" ca="1">YIELDMAT(DATE(2008,3,15),{1;2},DATE(2007,11,8),0.0625,100.0123,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B16">
@@ -2255,7 +2267,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="e" cm="1">
-        <f t="array" ref="A17">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),DATE(2007,11,8),0.0625,D!B1:B2,0)</f>
+        <f t="array" ref="A17">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),D!B1:B2,0.0625,100.0123,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B17">
@@ -2276,7 +2288,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A18" ca="1">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),DATE(2007,11,8),0.0625,{1;2},0)</f>
+        <f t="array" aca="1" ref="A18" ca="1">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),{1;2},0.0625,100.0123,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B18">
@@ -2297,7 +2309,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="e" cm="1">
-        <f t="array" ref="A19">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),DATE(2007,11,8),0.0625,100.0123,D!B1:B2)</f>
+        <f t="array" ref="A19">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),DATE(2007,11,8),D!B1:B2,100.0123,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B19">
@@ -2318,7 +2330,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A20" ca="1">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),DATE(2007,11,8),0.0625,100.0123,{1;2})</f>
+        <f t="array" aca="1" ref="A20" ca="1">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),DATE(2007,11,8),{1;2},100.0123,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B20">
@@ -2338,20 +2350,20 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A21" ca="1">_xlfn.Z.TEST(D!B1:B8,D!B1:B2)</f>
+      <c r="A21" t="e" cm="1">
+        <f t="array" ref="A21">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),DATE(2007,11,8),0.0625,D!B1:B2,0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B21">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C21">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D21" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="E21" t="s">
@@ -2360,7 +2372,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A22" ca="1">_xlfn.Z.TEST(D!B1:B8,{1;2})</f>
+        <f t="array" aca="1" ref="A22" ca="1">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),DATE(2007,11,8),0.0625,{1;2},0)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B22">
@@ -2380,20 +2392,20 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A23" ca="1">ZTEST(D!B1:B8,D!B1:B2)</f>
+      <c r="A23" t="e" cm="1">
+        <f t="array" ref="A23">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),DATE(2007,11,8),0.0625,100.0123,D!B1:B2)</f>
         <v>#VALUE!</v>
       </c>
       <c r="B23">
-        <f t="shared" ca="1" si="0"/>
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="C23">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D23" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="E23" t="s">
@@ -2402,7 +2414,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="e" cm="1" vm="1">
-        <f t="array" aca="1" ref="A24" ca="1">ZTEST(D!B1:B8,{1;2})</f>
+        <f t="array" aca="1" ref="A24" ca="1">YIELDMAT(DATE(2008,3,15),DATE(2008,11,3),DATE(2007,11,8),0.0625,100.0123,{1;2})</f>
         <v>#VALUE!</v>
       </c>
       <c r="B24">
@@ -2422,8 +2434,92 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="A25" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A25" ca="1">_xlfn.Z.TEST(D!B1:B8,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B25">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C25">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E25" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A26" ca="1">_xlfn.Z.TEST(D!B1:B8,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B26">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C26">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A27" ca="1">ZTEST(D!B1:B8,D!B1:B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B27">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C27">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D27" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="e" cm="1" vm="1">
+        <f t="array" aca="1" ref="A28" ca="1">ZTEST(D!B1:B8,{1;2})</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="B28">
+        <f t="shared" ca="1" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C28">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v/>
+      </c>
+      <c r="E28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
